--- a/docs/proposals/1.7-numbers-draft.xlsx
+++ b/docs/proposals/1.7-numbers-draft.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1169,6 +1169,179 @@
           <t>註：狩獵一次 −16 是自動玩家量到的平均（小獵物的撲抓很省、追鹿多回合很耗）；地形加成沒有算進去。</t>
         </is>
       </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>QA-55：最低體力規則（目前體力 0 仍能狩獵、練能力，只有追擊時體力不夠付才 −15%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>規則</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>目前</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>門檻／數值</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>你的意見</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>開始狩獵</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>任何體力都能開始</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>體力低於門檻不能開始狩獵，按鈕灰掉並寫「太累了，追不動」</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>太累時連追的力氣都沒有；避免體力 0 還連續狩獵</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>行動的能力成長</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>體力 0 也照常成長</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>體力低於門檻時，行動、狩獵帶來的能力成長 ×0.5</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>累到極點練不起來；鼓勵休息後再練</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>探索、採集、找睡處、移動</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>照常</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>照常可以做，體力最低停在 0</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>保留逃命、找睡處的路，不會卡死</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>戰鬥中體力 0</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>沒有影響</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>撲咬、猛撲的命中 −15%（和追擊的「太累」相同）</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>−15%</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>戰鬥中耗盡體力應該看得出來</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>頂部提示</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1.6 已加</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>體力 ≤ 門檻時頂部顯示「體力不支」</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>1.6 已實作（balance.stamina_low_threshold）</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
